--- a/ig/ch-epl/StructureDefinition-reimbursementSL.xlsx
+++ b/ig/ch-epl/StructureDefinition-reimbursementSL.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="195">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CH - EPL Reimbursement SL</t>
+    <t>CH EPL - Reimbursement SL</t>
   </si>
   <si>
     <t>Status</t>
@@ -292,7 +292,7 @@
     <t>Extension.extension</t>
   </si>
   <si>
-    <t>6</t>
+    <t>5</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
@@ -551,27 +551,6 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:productType</t>
-  </si>
-  <si>
-    <t>productType</t>
-  </si>
-  <si>
-    <t>The product type related to the reimbursement</t>
-  </si>
-  <si>
-    <t>Extension.extension:productType.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:productType.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:productType.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:productType.value[x]</t>
-  </si>
-  <si>
     <t>Extension.extension:gamme</t>
   </si>
   <si>
@@ -591,6 +570,31 @@
   </si>
   <si>
     <t>Extension.extension:gamme.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel</t>
+  </si>
+  <si>
+    <t>priceModel</t>
+  </si>
+  <si>
+    <t>Indicator for a Price Model</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
   </si>
   <si>
     <t>Extension.extension:productPrice</t>
@@ -603,7 +607,7 @@
 </t>
   </si>
   <si>
-    <t>CH - EPL Product Price</t>
+    <t>CH EPL - Product Price</t>
   </si>
   <si>
     <t>A set of information about the price of a drug</t>
@@ -1402,7 +1406,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>83</v>
@@ -5557,7 +5561,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6502,7 +6506,7 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>116</v>
@@ -6579,13 +6583,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -6607,13 +6611,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6815,7 +6819,7 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>116</v>
